--- a/stockcatcher/CB初級市場資訊20260727.xlsx
+++ b/stockcatcher/CB初級市場資訊20260727.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Jessica\CB初級市場資訊_New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m2994\Desktop\stockcatcher\stockcatcher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B35A5F-55DB-4652-8CD2-1C51DC11D201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D4C81F-1BF8-4A90-9075-A5EACCC1752F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63E94DED-069A-4779-8A4B-EA6B7F271FE9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{63E94DED-069A-4779-8A4B-EA6B7F271FE9}"/>
   </bookViews>
   <sheets>
     <sheet name="CB初級市場資訊" sheetId="1" r:id="rId1"/>
@@ -4700,18 +4700,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57934EC2-291D-4C15-BBF4-0E423859FB77}">
   <sheetPr codeName="工作表2"/>
   <dimension ref="A1:P1048387"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13.25" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="15.25" customWidth="1"/>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="20.75" customWidth="1"/>
-    <col min="9" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="13" width="13.625" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" customWidth="1"/>
+    <col min="10" max="13" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
@@ -4728,7 +4728,7 @@
       <c r="L1" s="49"/>
       <c r="M1" s="50"/>
     </row>
-    <row r="2" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:16" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="51" t="s">
         <v>2</v>
       </c>
@@ -4766,7 +4766,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="5"/>
     </row>
-    <row r="4" spans="1:16" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9">
         <v>80541</v>
       </c>
@@ -4851,7 +4851,7 @@
       <c r="N5" s="16"/>
       <c r="P5" s="17"/>
     </row>
-    <row r="6" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9">
         <v>24867</v>
       </c>
@@ -4895,7 +4895,7 @@
       <c r="N6" s="19"/>
       <c r="P6" s="17"/>
     </row>
-    <row r="7" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="9">
         <v>30285</v>
       </c>
@@ -4939,7 +4939,7 @@
       <c r="N7" s="19"/>
       <c r="P7" s="17"/>
     </row>
-    <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9">
         <v>68692</v>
       </c>
@@ -4983,7 +4983,7 @@
       <c r="N8" s="19"/>
       <c r="P8" s="17"/>
     </row>
-    <row r="9" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="9">
         <v>84423</v>
       </c>
@@ -5027,7 +5027,7 @@
       <c r="N9" s="19"/>
       <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9">
         <v>66931</v>
       </c>
@@ -5071,7 +5071,7 @@
       <c r="N10" s="19"/>
       <c r="P10" s="17"/>
     </row>
-    <row r="11" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="9">
         <v>69031</v>
       </c>
@@ -5115,7 +5115,7 @@
       <c r="N11" s="19"/>
       <c r="P11" s="17"/>
     </row>
-    <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21">
         <v>52912</v>
       </c>
@@ -5159,7 +5159,7 @@
       <c r="N12" s="19"/>
       <c r="P12" s="17"/>
     </row>
-    <row r="13" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21">
         <v>35833</v>
       </c>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="N13" s="19"/>
     </row>
-    <row r="14" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21">
         <v>81552</v>
       </c>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="N14" s="19"/>
     </row>
-    <row r="15" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="21">
         <v>55362</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>0.93803056027164688</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21">
         <v>84381</v>
       </c>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="N16" s="19"/>
     </row>
-    <row r="17" spans="1:14" s="6" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="6" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="21">
         <v>47642</v>
       </c>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="N17" s="5"/>
     </row>
-    <row r="18" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="21">
         <v>69032</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>0.92888047593293666</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="21">
         <v>66831</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>1.0247537929198829</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="21">
         <v>30811</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>1.0267933329540928</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="21">
         <v>81553</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>0.95754716981132071</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="21">
         <v>23031</v>
       </c>
@@ -5574,7 +5574,7 @@
       <c r="L22" s="25"/>
       <c r="M22" s="29"/>
     </row>
-    <row r="23" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="21">
         <v>31414</v>
       </c>
@@ -5607,7 +5607,7 @@
       <c r="L23" s="25"/>
       <c r="M23" s="29"/>
     </row>
-    <row r="24" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="31" t="s">
         <v>84</v>
       </c>
@@ -5624,7 +5624,7 @@
       <c r="L24" s="31"/>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" spans="1:14" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
         <v>3</v>
       </c>
@@ -5662,7 +5662,7 @@
       <c r="M25" s="4"/>
       <c r="N25" s="5"/>
     </row>
-    <row r="26" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20">
         <v>99354</v>
       </c>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="20">
         <v>12951</v>
       </c>
@@ -5738,7 +5738,7 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="20">
         <v>84424</v>
       </c>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M28" s="4"/>
     </row>
-    <row r="29" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="20">
         <v>82221</v>
       </c>
@@ -5814,7 +5814,7 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="20">
         <v>99589</v>
       </c>
@@ -5851,7 +5851,7 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
     </row>
-    <row r="31" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="20">
         <v>30062</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
     </row>
-    <row r="32" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="20">
         <v>30286</v>
       </c>
@@ -5925,7 +5925,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
     </row>
-    <row r="33" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="20">
         <v>25305</v>
       </c>
@@ -5962,7 +5962,7 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
     </row>
-    <row r="34" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="20">
         <v>31494</v>
       </c>
@@ -5999,7 +5999,7 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
     </row>
-    <row r="35" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="20">
         <v>35834</v>
       </c>
@@ -6036,7 +6036,7 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
     </row>
-    <row r="36" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="20">
         <v>35972</v>
       </c>
@@ -6073,7 +6073,7 @@
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
     </row>
-    <row r="37" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20">
         <v>24512</v>
       </c>
@@ -6110,7 +6110,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
     </row>
-    <row r="38" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="9">
         <v>23032</v>
       </c>
@@ -6147,7 +6147,7 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
     </row>
-    <row r="39" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="9">
         <v>55363</v>
       </c>
@@ -6184,7 +6184,7 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
     </row>
-    <row r="40" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="9">
         <v>35122</v>
       </c>
@@ -6221,7 +6221,7 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
     </row>
-    <row r="41" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="9">
         <v>30812</v>
       </c>
@@ -6258,7 +6258,7 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
     </row>
-    <row r="42" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="9">
         <v>89365</v>
       </c>
@@ -6295,7 +6295,7 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
     </row>
-    <row r="43" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="9">
         <v>89366</v>
       </c>
@@ -6332,7 +6332,7 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
     </row>
-    <row r="44" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="9">
         <v>31415</v>
       </c>
@@ -6369,7 +6369,7 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
     </row>
-    <row r="45" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="21">
         <v>49675</v>
       </c>
@@ -6406,7 +6406,7 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
     </row>
-    <row r="46" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="21">
         <v>65702</v>
       </c>
@@ -6443,7 +6443,7 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
     </row>
-    <row r="47" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="21">
         <v>30166</v>
       </c>
@@ -6480,7 +6480,7 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
     </row>
-    <row r="48" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="21">
         <v>32191</v>
       </c>
@@ -6517,7 +6517,7 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
     </row>
-    <row r="49" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="21">
         <v>24643</v>
       </c>
@@ -6554,7 +6554,7 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
     </row>
-    <row r="50" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="21">
         <v>49731</v>
       </c>
@@ -6591,7 +6591,7 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
     </row>
-    <row r="51" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="21">
         <v>84223</v>
       </c>
@@ -6628,7 +6628,7 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
     </row>
-    <row r="52" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="21">
         <v>77381</v>
       </c>
@@ -6665,7 +6665,7 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="21">
         <v>76311</v>
       </c>
@@ -6702,7 +6702,7 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
     </row>
-    <row r="54" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="21">
         <v>89162</v>
       </c>
@@ -6739,7 +6739,7 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
     </row>
-    <row r="55" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="21">
         <v>15602</v>
       </c>
@@ -6776,7 +6776,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
     </row>
-    <row r="56" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="53" t="s">
         <v>168</v>
       </c>
@@ -6793,7 +6793,7 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
     </row>
-    <row r="57" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="7" t="s">
         <v>3</v>
       </c>
@@ -6828,7 +6828,7 @@
       <c r="L57" s="43"/>
       <c r="M57" s="44"/>
     </row>
-    <row r="58" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="20">
         <v>37013</v>
       </c>
@@ -6863,7 +6863,7 @@
       <c r="L58" s="46"/>
       <c r="M58" s="4"/>
     </row>
-    <row r="59" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="20">
         <v>84674</v>
       </c>
@@ -6898,7 +6898,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
     </row>
-    <row r="60" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="20">
         <v>84675</v>
       </c>
@@ -6933,7 +6933,7 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
     </row>
-    <row r="61" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="9">
         <v>27621</v>
       </c>
@@ -6968,7 +6968,7 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
     </row>
-    <row r="62" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="9">
         <v>26461</v>
       </c>
@@ -7003,9 +7003,9 @@
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
     </row>
-    <row r="63" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="9">
-        <v>24642</v>
+        <v>26462</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>186</v>
@@ -7036,7 +7036,7 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
     </row>
-    <row r="64" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="9">
         <v>52636</v>
       </c>
@@ -7071,7 +7071,7 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
     </row>
-    <row r="65" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="9">
         <v>45415</v>
       </c>
@@ -7106,7 +7106,7 @@
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
     </row>
-    <row r="66" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="9">
         <v>45416</v>
       </c>
@@ -7141,7 +7141,7 @@
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
     </row>
-    <row r="67" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="9">
         <v>23161</v>
       </c>
@@ -7176,7 +7176,7 @@
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
     </row>
-    <row r="68" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="9">
         <v>33395</v>
       </c>
@@ -7211,7 +7211,7 @@
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
     </row>
-    <row r="69" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="9">
         <v>65971</v>
       </c>
@@ -7246,7 +7246,7 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
     </row>
-    <row r="70" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -7261,7 +7261,7 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
     </row>
-    <row r="71" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -7276,7 +7276,7 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
     </row>
-    <row r="72" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -7291,7 +7291,7 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -7306,7 +7306,7 @@
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
     </row>
-    <row r="74" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -7321,7 +7321,7 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -7336,7 +7336,7 @@
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
     </row>
-    <row r="76" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -7351,7 +7351,7 @@
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
     </row>
-    <row r="77" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -7366,7 +7366,7 @@
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
     </row>
-    <row r="78" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -7381,7 +7381,7 @@
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
     </row>
-    <row r="79" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -7396,7 +7396,7 @@
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
     </row>
-    <row r="80" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -7411,7 +7411,7 @@
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
     </row>
-    <row r="81" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -7426,7 +7426,7 @@
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
     </row>
-    <row r="82" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -7441,7 +7441,7 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
     </row>
-    <row r="83" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -7456,7 +7456,7 @@
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
     </row>
-    <row r="84" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -7471,7 +7471,7 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
     </row>
-    <row r="85" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -7486,7 +7486,7 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
     </row>
-    <row r="86" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -7501,7 +7501,7 @@
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -7516,7 +7516,7 @@
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
     </row>
-    <row r="88" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -7531,7 +7531,7 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -7546,7 +7546,7 @@
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
     </row>
-    <row r="90" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -7561,7 +7561,7 @@
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
     </row>
-    <row r="91" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -7576,7 +7576,7 @@
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
     </row>
-    <row r="92" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -7591,7 +7591,7 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
     </row>
-    <row r="93" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -7606,7 +7606,7 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
     </row>
-    <row r="94" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -7621,7 +7621,7 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
     </row>
-    <row r="95" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -7636,7 +7636,7 @@
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
     </row>
-    <row r="96" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -7651,7 +7651,7 @@
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
     </row>
-    <row r="97" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -7666,7 +7666,7 @@
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
     </row>
-    <row r="98" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -7681,7 +7681,7 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
     </row>
-    <row r="99" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -7696,7 +7696,7 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
     </row>
-    <row r="100" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -7711,7 +7711,7 @@
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
     </row>
-    <row r="101" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -7726,7 +7726,7 @@
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
     </row>
-    <row r="102" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -7741,7 +7741,7 @@
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
     </row>
-    <row r="103" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -7756,7 +7756,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
     </row>
-    <row r="104" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -7771,7 +7771,7 @@
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
     </row>
-    <row r="105" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -7786,7 +7786,7 @@
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
     </row>
-    <row r="106" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -7801,7 +7801,7 @@
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
     </row>
-    <row r="107" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -7816,7 +7816,7 @@
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
     </row>
-    <row r="108" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -7831,7 +7831,7 @@
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
     </row>
-    <row r="109" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -7846,7 +7846,7 @@
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
     </row>
-    <row r="110" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -7861,7 +7861,7 @@
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
     </row>
-    <row r="111" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -7876,7 +7876,7 @@
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
     </row>
-    <row r="112" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -7891,7 +7891,7 @@
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
     </row>
-    <row r="113" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -7906,7 +7906,7 @@
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
     </row>
-    <row r="114" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -7921,7 +7921,7 @@
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
     </row>
-    <row r="115" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -7936,7 +7936,7 @@
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
     </row>
-    <row r="116" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -7951,7 +7951,7 @@
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
     </row>
-    <row r="117" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -7966,7 +7966,7 @@
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
     </row>
-    <row r="118" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -7981,7 +7981,7 @@
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
     </row>
-    <row r="119" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -7996,7 +7996,7 @@
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
     </row>
-    <row r="120" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -8011,7 +8011,7 @@
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
     </row>
-    <row r="121" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -8026,7 +8026,7 @@
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
     </row>
-    <row r="122" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -8041,7 +8041,7 @@
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
     </row>
-    <row r="123" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -8056,7 +8056,7 @@
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
     </row>
-    <row r="124" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -8071,7 +8071,7 @@
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
     </row>
-    <row r="125" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -8086,7 +8086,7 @@
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
     </row>
-    <row r="126" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -8101,7 +8101,7 @@
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
     </row>
-    <row r="127" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -8116,7 +8116,7 @@
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
     </row>
-    <row r="128" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -8131,7 +8131,7 @@
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
     </row>
-    <row r="129" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -8146,7 +8146,7 @@
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
     </row>
-    <row r="130" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -8161,7 +8161,7 @@
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
     </row>
-    <row r="131" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -8176,7 +8176,7 @@
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
     </row>
-    <row r="132" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -8191,7 +8191,7 @@
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
     </row>
-    <row r="133" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -8206,7 +8206,7 @@
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
     </row>
-    <row r="134" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -8221,7 +8221,7 @@
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
     </row>
-    <row r="135" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -8236,7 +8236,7 @@
       <c r="L135" s="4"/>
       <c r="M135" s="4"/>
     </row>
-    <row r="136" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -8251,7 +8251,7 @@
       <c r="L136" s="4"/>
       <c r="M136" s="4"/>
     </row>
-    <row r="137" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -8266,7 +8266,7 @@
       <c r="L137" s="4"/>
       <c r="M137" s="4"/>
     </row>
-    <row r="138" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -8281,7 +8281,7 @@
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
     </row>
-    <row r="139" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -8296,7 +8296,7 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
     </row>
-    <row r="140" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -8311,7 +8311,7 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
     </row>
-    <row r="141" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -8326,7 +8326,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
     </row>
-    <row r="142" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -8341,7 +8341,7 @@
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
     </row>
-    <row r="143" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -8356,7 +8356,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
     </row>
-    <row r="144" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -8371,7 +8371,7 @@
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
     </row>
-    <row r="145" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -8386,7 +8386,7 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
     </row>
-    <row r="146" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -8401,7 +8401,7 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
     </row>
-    <row r="147" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -8416,7 +8416,7 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
     </row>
-    <row r="148" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -8431,7 +8431,7 @@
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
     </row>
-    <row r="149" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -8446,7 +8446,7 @@
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
     </row>
-    <row r="150" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -8461,7 +8461,7 @@
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
     </row>
-    <row r="151" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -8476,7 +8476,7 @@
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
     </row>
-    <row r="152" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -8491,7 +8491,7 @@
       <c r="L152" s="4"/>
       <c r="M152" s="4"/>
     </row>
-    <row r="153" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -8506,7 +8506,7 @@
       <c r="L153" s="4"/>
       <c r="M153" s="4"/>
     </row>
-    <row r="154" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -8521,7 +8521,7 @@
       <c r="L154" s="4"/>
       <c r="M154" s="4"/>
     </row>
-    <row r="155" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -8536,7 +8536,7 @@
       <c r="L155" s="4"/>
       <c r="M155" s="4"/>
     </row>
-    <row r="156" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -8551,7 +8551,7 @@
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
     </row>
-    <row r="157" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -8566,7 +8566,7 @@
       <c r="L157" s="4"/>
       <c r="M157" s="4"/>
     </row>
-    <row r="158" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -8581,7 +8581,7 @@
       <c r="L158" s="4"/>
       <c r="M158" s="4"/>
     </row>
-    <row r="159" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -8596,7 +8596,7 @@
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
     </row>
-    <row r="160" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -8611,7 +8611,7 @@
       <c r="L160" s="4"/>
       <c r="M160" s="4"/>
     </row>
-    <row r="161" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -8626,7 +8626,7 @@
       <c r="L161" s="4"/>
       <c r="M161" s="4"/>
     </row>
-    <row r="162" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -8641,7 +8641,7 @@
       <c r="L162" s="4"/>
       <c r="M162" s="4"/>
     </row>
-    <row r="163" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -8656,7 +8656,7 @@
       <c r="L163" s="4"/>
       <c r="M163" s="4"/>
     </row>
-    <row r="164" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -8671,7 +8671,7 @@
       <c r="L164" s="4"/>
       <c r="M164" s="4"/>
     </row>
-    <row r="165" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -8686,7 +8686,7 @@
       <c r="L165" s="4"/>
       <c r="M165" s="4"/>
     </row>
-    <row r="166" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -8701,7 +8701,7 @@
       <c r="L166" s="4"/>
       <c r="M166" s="4"/>
     </row>
-    <row r="167" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -8716,7 +8716,7 @@
       <c r="L167" s="4"/>
       <c r="M167" s="4"/>
     </row>
-    <row r="168" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -8731,7 +8731,7 @@
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
     </row>
-    <row r="169" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -8746,7 +8746,7 @@
       <c r="L169" s="4"/>
       <c r="M169" s="4"/>
     </row>
-    <row r="170" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -8761,7 +8761,7 @@
       <c r="L170" s="4"/>
       <c r="M170" s="4"/>
     </row>
-    <row r="171" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -8776,7 +8776,7 @@
       <c r="L171" s="4"/>
       <c r="M171" s="4"/>
     </row>
-    <row r="172" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -8791,7 +8791,7 @@
       <c r="L172" s="4"/>
       <c r="M172" s="4"/>
     </row>
-    <row r="173" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -8806,7 +8806,7 @@
       <c r="L173" s="4"/>
       <c r="M173" s="4"/>
     </row>
-    <row r="174" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -8821,7 +8821,7 @@
       <c r="L174" s="4"/>
       <c r="M174" s="4"/>
     </row>
-    <row r="175" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -8836,7 +8836,7 @@
       <c r="L175" s="4"/>
       <c r="M175" s="4"/>
     </row>
-    <row r="176" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -8851,7 +8851,7 @@
       <c r="L176" s="4"/>
       <c r="M176" s="4"/>
     </row>
-    <row r="177" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -8866,7 +8866,7 @@
       <c r="L177" s="4"/>
       <c r="M177" s="4"/>
     </row>
-    <row r="178" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -8881,7 +8881,7 @@
       <c r="L178" s="4"/>
       <c r="M178" s="4"/>
     </row>
-    <row r="179" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -8896,7 +8896,7 @@
       <c r="L179" s="4"/>
       <c r="M179" s="4"/>
     </row>
-    <row r="180" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -8911,7 +8911,7 @@
       <c r="L180" s="4"/>
       <c r="M180" s="4"/>
     </row>
-    <row r="181" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -8926,7 +8926,7 @@
       <c r="L181" s="4"/>
       <c r="M181" s="4"/>
     </row>
-    <row r="182" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -8941,7 +8941,7 @@
       <c r="L182" s="4"/>
       <c r="M182" s="4"/>
     </row>
-    <row r="183" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -8956,7 +8956,7 @@
       <c r="L183" s="4"/>
       <c r="M183" s="4"/>
     </row>
-    <row r="184" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -8971,7 +8971,7 @@
       <c r="L184" s="4"/>
       <c r="M184" s="4"/>
     </row>
-    <row r="185" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -8986,7 +8986,7 @@
       <c r="L185" s="4"/>
       <c r="M185" s="4"/>
     </row>
-    <row r="186" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -9001,7 +9001,7 @@
       <c r="L186" s="4"/>
       <c r="M186" s="4"/>
     </row>
-    <row r="187" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -9016,7 +9016,7 @@
       <c r="L187" s="4"/>
       <c r="M187" s="4"/>
     </row>
-    <row r="188" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -9031,7 +9031,7 @@
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
     </row>
-    <row r="189" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -9046,7 +9046,7 @@
       <c r="L189" s="4"/>
       <c r="M189" s="4"/>
     </row>
-    <row r="190" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -9061,7 +9061,7 @@
       <c r="L190" s="4"/>
       <c r="M190" s="4"/>
     </row>
-    <row r="191" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -9076,7 +9076,7 @@
       <c r="L191" s="4"/>
       <c r="M191" s="4"/>
     </row>
-    <row r="192" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -9091,7 +9091,7 @@
       <c r="L192" s="4"/>
       <c r="M192" s="4"/>
     </row>
-    <row r="193" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -9106,7 +9106,7 @@
       <c r="L193" s="4"/>
       <c r="M193" s="4"/>
     </row>
-    <row r="194" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -9121,7 +9121,7 @@
       <c r="L194" s="4"/>
       <c r="M194" s="4"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -9136,7 +9136,7 @@
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -9151,7 +9151,7 @@
       <c r="L196" s="4"/>
       <c r="M196" s="4"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -9166,7 +9166,7 @@
       <c r="L197" s="4"/>
       <c r="M197" s="4"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -9181,7 +9181,7 @@
       <c r="L198" s="4"/>
       <c r="M198" s="4"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -9196,7 +9196,7 @@
       <c r="L199" s="4"/>
       <c r="M199" s="4"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -9211,7 +9211,7 @@
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
     </row>
-    <row r="1048387" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="1048387" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H1048387" s="20"/>
     </row>
   </sheetData>
